--- a/unified_service/database/tables/Сравнение Embedding-моделей для RAG.xlsx
+++ b/unified_service/database/tables/Сравнение Embedding-моделей для RAG.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="292">
   <si>
     <t>Страна</t>
   </si>
@@ -143,7 +143,7 @@
     <t>Фев 2024</t>
   </si>
   <si>
-    <t>~63.2</t>
+    <t>63.2</t>
   </si>
   <si>
     <t>Топ-40 / Топ-15</t>
@@ -197,7 +197,7 @@
     <t>text-embedding-v3</t>
   </si>
   <si>
-    <t>~65.0</t>
+    <t>65.0</t>
   </si>
   <si>
     <t>Топ-20 / Топ-15</t>
@@ -470,7 +470,7 @@
     <t>GritLM-7B</t>
   </si>
   <si>
-    <t>~66.8</t>
+    <t>66.8</t>
   </si>
   <si>
     <t>Топ-15 / Топ-20</t>
@@ -500,7 +500,7 @@
     <t>Март 2024</t>
   </si>
   <si>
-    <t>~64.6</t>
+    <t>64.6</t>
   </si>
   <si>
     <t>Топ-25 / Не применимо (EN)</t>
@@ -575,7 +575,7 @@
     <t>NV-Embed-v2</t>
   </si>
   <si>
-    <t xml:space="preserve">~69.3 </t>
+    <t xml:space="preserve">69.3 </t>
   </si>
   <si>
     <t>Топ-1 / Топ-5</t>
@@ -608,7 +608,7 @@
     <t>nomic-embed-text-v1.5</t>
   </si>
   <si>
-    <t>~62.4</t>
+    <t>62.4</t>
   </si>
   <si>
     <t>Топ-50 / Не применимо (EN)</t>
@@ -692,7 +692,7 @@
     <t>SFR-Embedding-2_R</t>
   </si>
   <si>
-    <t>~67.6</t>
+    <t>67.6</t>
   </si>
   <si>
     <t>Топ-10 / Не применимо (EN)</t>
@@ -719,7 +719,7 @@
     <t>multilingual-e5-large</t>
   </si>
   <si>
-    <t>~61.4</t>
+    <t>61.4</t>
   </si>
   <si>
     <t>Топ-70 / Топ-20</t>
@@ -749,7 +749,7 @@
     <t>multilingual-e5-small</t>
   </si>
   <si>
-    <t>~57.5</t>
+    <t>57.5</t>
   </si>
   <si>
     <t>Топ-100 / Топ-30</t>
@@ -821,9 +821,6 @@
     <t>text-embedding-3-large</t>
   </si>
   <si>
-    <t>64.6</t>
-  </si>
-  <si>
     <t>Топ-25 / Топ-15</t>
   </si>
   <si>
@@ -914,7 +911,7 @@
     <t>text-multilingual-embedding-002</t>
   </si>
   <si>
-    <t>~63.0</t>
+    <t>63.0</t>
   </si>
   <si>
     <t>Топ-50 / Топ-20</t>
@@ -983,7 +980,7 @@
     <t>snowflake-arctic-embed-l-v2.0</t>
   </si>
   <si>
-    <t>~64.8</t>
+    <t>64.8</t>
   </si>
   <si>
     <r>
@@ -1004,7 +1001,7 @@
     <t>granite-embedding-278m-multilingual</t>
   </si>
   <si>
-    <t>~62.5</t>
+    <t>62.5</t>
   </si>
   <si>
     <t>~1GB / ~2GB VRAM</t>
@@ -1028,7 +1025,7 @@
     <t>amazon.titan-embed-text-v2:0</t>
   </si>
   <si>
-    <t>~64.0</t>
+    <t>64.0</t>
   </si>
   <si>
     <t>Топ-40 / Не применимо</t>
@@ -1127,9 +1124,6 @@
     <t>embed-multilingual-v4.0</t>
   </si>
   <si>
-    <t>66.8</t>
-  </si>
-  <si>
     <t>Топ-10 / Топ-5</t>
   </si>
   <si>
@@ -1154,7 +1148,7 @@
     <t>mistral-embed</t>
   </si>
   <si>
-    <t>~62.0</t>
+    <t>62.0</t>
   </si>
   <si>
     <t>Топ-60 / Топ-30</t>
@@ -2351,7 +2345,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2365,7 +2359,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2379,7 +2373,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2393,7 +2387,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2407,7 +2401,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2421,7 +2415,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2435,7 +2429,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2449,7 +2443,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2463,7 +2457,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2477,7 +2471,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2491,7 +2485,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2505,7 +2499,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -2558,7 +2552,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Сравнение Embedding-моделей для-style" pivot="0" count="4" xr9:uid="{6BCE1530-303D-4B51-8CF0-458F56EFCFBD}">
+    <tableStyle name="Сравнение Embedding-моделей для-style" pivot="0" count="4" xr9:uid="{9F6CA9C8-A345-4C12-BE92-BCFE5A35F5E5}">
       <tableStyleElement type="wholeTable" dxfId="15"/>
       <tableStyleElement type="headerRow" dxfId="14"/>
       <tableStyleElement type="firstRowStripe" dxfId="13"/>
@@ -2794,17 +2788,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S1042"/>
-  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6333333333333" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="29.8796296296296" customWidth="1"/>
+    <col min="1" max="3" width="29.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="15.75" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="33.6296296296296" customWidth="1"/>
-    <col min="7" max="7" width="16.3796296296296" customWidth="1"/>
+    <col min="6" max="6" width="33.6333333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.3833333333333" customWidth="1"/>
     <col min="8" max="8" width="19.75" customWidth="1"/>
     <col min="9" max="9" width="23.25" customWidth="1"/>
-    <col min="10" max="10" width="29.1296296296296" customWidth="1"/>
-    <col min="11" max="11" width="37.6296296296296" customWidth="1"/>
+    <col min="10" max="10" width="29.1333333333333" customWidth="1"/>
+    <col min="11" max="11" width="37.6333333333333" customWidth="1"/>
     <col min="12" max="12" width="50.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4146,28 +4140,28 @@
         <v>45292</v>
       </c>
       <c r="E41" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="G41" s="17" t="s">
         <v>184</v>
-      </c>
-      <c r="G41" s="17" t="s">
-        <v>185</v>
       </c>
       <c r="H41" s="17">
         <v>8192</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J41" s="16" t="s">
         <v>34</v>
       </c>
       <c r="K41" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="L41" s="23" t="s">
         <v>187</v>
-      </c>
-      <c r="L41" s="23" t="s">
-        <v>188</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
@@ -4178,7 +4172,7 @@
       <c r="A42" s="14"/>
       <c r="B42" s="15"/>
       <c r="C42" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D42" s="25">
         <v>46023</v>
@@ -4187,25 +4181,25 @@
         <v>52</v>
       </c>
       <c r="F42" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="G42" s="28" t="s">
         <v>190</v>
-      </c>
-      <c r="G42" s="28" t="s">
-        <v>191</v>
       </c>
       <c r="H42" s="28" t="s">
         <v>81</v>
       </c>
       <c r="I42" s="46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J42" s="27" t="s">
         <v>34</v>
       </c>
       <c r="K42" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
@@ -4216,7 +4210,7 @@
       <c r="A43" s="14"/>
       <c r="B43" s="20"/>
       <c r="C43" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D43" s="22">
         <v>45292</v>
@@ -4225,32 +4219,32 @@
         <v>75</v>
       </c>
       <c r="F43" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="G43" s="17" t="s">
         <v>194</v>
-      </c>
-      <c r="G43" s="17" t="s">
-        <v>195</v>
       </c>
       <c r="H43" s="17">
         <v>8192</v>
       </c>
       <c r="I43" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J43" s="16" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="L43" s="31" t="s">
         <v>187</v>
-      </c>
-      <c r="L43" s="31" t="s">
-        <v>188</v>
       </c>
       <c r="P43" s="7"/>
     </row>
     <row r="44" ht="22.5" customHeight="1" spans="1:19">
       <c r="A44" s="14"/>
       <c r="B44" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C44" s="10"/>
       <c r="D44" s="11"/>
@@ -4263,32 +4257,32 @@
       <c r="K44" s="10"/>
       <c r="L44" s="13"/>
       <c r="P44" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1" spans="1:19">
       <c r="A45" s="14"/>
       <c r="B45" s="15"/>
       <c r="C45" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D45" s="17" t="s">
         <v>198</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>199</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>80</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H45" s="17">
         <v>8192</v>
       </c>
       <c r="I45" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J45" s="16" t="s">
         <v>34</v>
@@ -4297,7 +4291,7 @@
         <v>47</v>
       </c>
       <c r="L45" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N45" s="45"/>
     </row>
@@ -4305,25 +4299,25 @@
       <c r="A46" s="14"/>
       <c r="B46" s="15"/>
       <c r="C46" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="D46" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="D46" s="28" t="s">
+      <c r="E46" s="26" t="s">
         <v>204</v>
-      </c>
-      <c r="E46" s="26" t="s">
-        <v>205</v>
       </c>
       <c r="F46" s="27" t="s">
         <v>18</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H46" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I46" s="46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J46" s="27" t="s">
         <v>55</v>
@@ -4332,7 +4326,7 @@
         <v>47</v>
       </c>
       <c r="L46" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N46" s="45"/>
     </row>
@@ -4340,16 +4334,16 @@
       <c r="A47" s="14"/>
       <c r="B47" s="20"/>
       <c r="C47" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D47" s="17">
         <v>2023</v>
       </c>
       <c r="E47" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="F47" s="16" t="s">
         <v>208</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>209</v>
       </c>
       <c r="G47" s="17">
         <v>768</v>
@@ -4358,7 +4352,7 @@
         <v>8192</v>
       </c>
       <c r="I47" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J47" s="16" t="s">
         <v>34</v>
@@ -4367,13 +4361,13 @@
         <v>47</v>
       </c>
       <c r="L47" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1" spans="1:19">
       <c r="A48" s="14"/>
       <c r="B48" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="11"/>
@@ -4386,32 +4380,32 @@
       <c r="K48" s="10"/>
       <c r="L48" s="13"/>
       <c r="P48" s="45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1" spans="1:12">
       <c r="A49" s="14"/>
       <c r="B49" s="15"/>
       <c r="C49" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>16</v>
       </c>
       <c r="E49" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G49" s="17" t="s">
         <v>213</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G49" s="17" t="s">
-        <v>214</v>
       </c>
       <c r="H49" s="17">
         <v>32000</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J49" s="16" t="s">
         <v>34</v>
@@ -4420,23 +4414,23 @@
         <v>47</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1" spans="1:12">
       <c r="A50" s="14"/>
       <c r="B50" s="15"/>
       <c r="C50" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D50" s="22">
         <v>45383</v>
       </c>
       <c r="E50" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="G50" s="17">
         <v>1024</v>
@@ -4445,41 +4439,41 @@
         <v>16000</v>
       </c>
       <c r="I50" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J50" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>47</v>
       </c>
       <c r="L50" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1" spans="1:12">
       <c r="A51" s="14"/>
       <c r="B51" s="15"/>
       <c r="C51" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D51" s="28" t="s">
         <v>146</v>
       </c>
       <c r="E51" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="F51" s="27" t="s">
+      <c r="G51" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="G51" s="28" t="s">
-        <v>223</v>
-      </c>
       <c r="H51" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I51" s="46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J51" s="27" t="s">
         <v>34</v>
@@ -4488,23 +4482,23 @@
         <v>47</v>
       </c>
       <c r="L51" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1" spans="1:12">
       <c r="A52" s="14"/>
       <c r="B52" s="20"/>
       <c r="C52" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D52" s="22">
         <v>45383</v>
       </c>
       <c r="E52" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F52" s="16" t="s">
         <v>217</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>218</v>
       </c>
       <c r="G52" s="17">
         <v>1024</v>
@@ -4513,22 +4507,22 @@
         <v>32000</v>
       </c>
       <c r="I52" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J52" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K52" s="9" t="s">
         <v>47</v>
       </c>
       <c r="L52" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1" spans="1:12">
       <c r="A53" s="14"/>
       <c r="B53" s="48" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="11"/>
@@ -4545,13 +4539,13 @@
       <c r="A54" s="14"/>
       <c r="B54" s="20"/>
       <c r="C54" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D54" s="22">
         <v>45383</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F54" s="16" t="s">
         <v>113</v>
@@ -4572,13 +4566,13 @@
         <v>27</v>
       </c>
       <c r="L54" s="31" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1" spans="1:12">
       <c r="A55" s="14"/>
       <c r="B55" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="11"/>
@@ -4595,16 +4589,16 @@
       <c r="A56" s="14"/>
       <c r="B56" s="20"/>
       <c r="C56" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D56" s="22">
         <v>45627</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G56" s="17">
         <v>768</v>
@@ -4619,16 +4613,16 @@
         <v>34</v>
       </c>
       <c r="K56" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="L56" s="31" t="s">
         <v>233</v>
-      </c>
-      <c r="L56" s="31" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1" spans="1:12">
       <c r="A57" s="14"/>
       <c r="B57" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="11"/>
@@ -4645,40 +4639,40 @@
       <c r="A58" s="14"/>
       <c r="B58" s="20"/>
       <c r="C58" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D58" s="22">
         <v>45383</v>
       </c>
       <c r="E58" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="F58" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="F58" s="16" t="s">
-        <v>238</v>
-      </c>
       <c r="G58" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H58" s="17">
         <v>8192</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J58" s="16" t="s">
         <v>67</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1" spans="1:12">
       <c r="A59" s="14"/>
       <c r="B59" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="11"/>
@@ -4695,13 +4689,13 @@
       <c r="A60" s="14"/>
       <c r="B60" s="20"/>
       <c r="C60" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D60" s="22">
         <v>45231</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F60" s="16" t="s">
         <v>122</v>
@@ -4719,16 +4713,16 @@
         <v>67</v>
       </c>
       <c r="K60" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="L60" s="31" t="s">
         <v>243</v>
-      </c>
-      <c r="L60" s="31" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1" spans="1:12">
       <c r="A61" s="14"/>
       <c r="B61" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="11"/>
@@ -4745,16 +4739,16 @@
       <c r="A62" s="35"/>
       <c r="B62" s="20"/>
       <c r="C62" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D62" s="17">
         <v>2022</v>
       </c>
       <c r="E62" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="F62" s="16" t="s">
         <v>247</v>
-      </c>
-      <c r="F62" s="16" t="s">
-        <v>248</v>
       </c>
       <c r="G62" s="17">
         <v>768</v>
@@ -4763,7 +4757,7 @@
         <v>512</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J62" s="51" t="s">
         <v>67</v>
@@ -4772,15 +4766,15 @@
         <v>72</v>
       </c>
       <c r="L62" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1" spans="1:12">
       <c r="A63" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B63" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="11"/>
@@ -4797,16 +4791,16 @@
       <c r="A64" s="14"/>
       <c r="B64" s="15"/>
       <c r="C64" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D64" s="22">
         <v>45231</v>
       </c>
       <c r="E64" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="F64" s="16" t="s">
         <v>254</v>
-      </c>
-      <c r="F64" s="16" t="s">
-        <v>255</v>
       </c>
       <c r="G64" s="17">
         <v>1024</v>
@@ -4815,7 +4809,7 @@
         <v>512</v>
       </c>
       <c r="I64" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J64" s="16" t="s">
         <v>55</v>
@@ -4824,57 +4818,57 @@
         <v>47</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1" spans="1:12">
       <c r="A65" s="14"/>
       <c r="B65" s="15"/>
       <c r="C65" s="27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D65" s="25">
         <v>45870</v>
       </c>
       <c r="E65" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F65" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="G65" s="28" t="s">
         <v>258</v>
-      </c>
-      <c r="F65" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="G65" s="28" t="s">
-        <v>260</v>
       </c>
       <c r="H65" s="28">
         <v>8192</v>
       </c>
       <c r="I65" s="46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J65" s="27" t="s">
         <v>55</v>
       </c>
       <c r="K65" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1" spans="1:12">
       <c r="A66" s="35"/>
       <c r="B66" s="20"/>
       <c r="C66" s="16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D66" s="22">
         <v>45231</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G66" s="17">
         <v>1024</v>
@@ -4883,7 +4877,7 @@
         <v>512</v>
       </c>
       <c r="I66" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J66" s="16" t="s">
         <v>67</v>
@@ -4892,15 +4886,15 @@
         <v>47</v>
       </c>
       <c r="L66" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1" spans="1:12">
       <c r="A67" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="11"/>
@@ -4917,16 +4911,16 @@
       <c r="A68" s="35"/>
       <c r="B68" s="20"/>
       <c r="C68" s="13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D68" s="22">
         <v>45261</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G68" s="17">
         <v>1024</v>
@@ -4935,7 +4929,7 @@
         <v>8192</v>
       </c>
       <c r="I68" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J68" s="16" t="s">
         <v>34</v>
@@ -4944,15 +4938,15 @@
         <v>47</v>
       </c>
       <c r="L68" s="31" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1" spans="1:12">
       <c r="A69" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="11"/>
@@ -4969,16 +4963,16 @@
       <c r="A70" s="14"/>
       <c r="B70" s="20"/>
       <c r="C70" s="13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D70" s="17">
         <v>2021</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G70" s="17">
         <v>1024</v>
@@ -4990,19 +4984,19 @@
         <v>61</v>
       </c>
       <c r="J70" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="L70" s="31" t="s">
         <v>275</v>
-      </c>
-      <c r="K70" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="L70" s="31" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1" spans="1:12">
       <c r="A71" s="14"/>
       <c r="B71" s="9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="11"/>
@@ -5019,40 +5013,40 @@
       <c r="A72" s="14"/>
       <c r="B72" s="20"/>
       <c r="C72" s="13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D72" s="22">
         <v>45352</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H72" s="17">
         <v>8192</v>
       </c>
       <c r="I72" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J72" s="16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K72" s="9" t="s">
         <v>47</v>
       </c>
       <c r="L72" s="31" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1" spans="1:12">
       <c r="A73" s="14"/>
       <c r="B73" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="11"/>
@@ -5069,16 +5063,16 @@
       <c r="A74" s="35"/>
       <c r="B74" s="20"/>
       <c r="C74" s="13" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D74" s="17">
         <v>2020</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G74" s="17">
         <v>768</v>
@@ -5090,21 +5084,21 @@
         <v>61</v>
       </c>
       <c r="J74" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="L74" s="31" t="s">
         <v>286</v>
-      </c>
-      <c r="K74" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="L74" s="31" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1" spans="1:12">
       <c r="A75" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="11"/>
@@ -5121,13 +5115,13 @@
       <c r="A76" s="35"/>
       <c r="B76" s="20"/>
       <c r="C76" s="13" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D76" s="22">
         <v>45292</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>86</v>
@@ -5139,7 +5133,7 @@
         <v>4096</v>
       </c>
       <c r="I76" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J76" s="16" t="s">
         <v>107</v>
@@ -5148,7 +5142,7 @@
         <v>47</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1" spans="1:12">
